--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/200.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/200.xlsx
@@ -426,13 +426,13 @@
         <v>-3.529389901851402</v>
       </c>
       <c r="E2">
-        <v>-14.61459680201989</v>
+        <v>-15.85530811064142</v>
       </c>
       <c r="F2">
-        <v>-2.205277361878143</v>
+        <v>-3.120475064206496</v>
       </c>
       <c r="G2">
-        <v>-9.567431411524515</v>
+        <v>-8.737110174274369</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.795754074365322</v>
       </c>
       <c r="E3">
-        <v>-16.10081480049326</v>
+        <v>-16.61357844085578</v>
       </c>
       <c r="F3">
-        <v>-2.097268192961921</v>
+        <v>-3.50739802274752</v>
       </c>
       <c r="G3">
-        <v>-8.321553945457353</v>
+        <v>-9.184053685349214</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.077070585256864</v>
       </c>
       <c r="E4">
-        <v>-17.26224158618849</v>
+        <v>-16.6448203830347</v>
       </c>
       <c r="F4">
-        <v>-2.185121526233226</v>
+        <v>-3.240839332935472</v>
       </c>
       <c r="G4">
-        <v>-9.68669381457676</v>
+        <v>-8.610693682311759</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.326733420401331</v>
       </c>
       <c r="E5">
-        <v>-17.348146738114</v>
+        <v>-17.98504943644879</v>
       </c>
       <c r="F5">
-        <v>-2.311179992489046</v>
+        <v>-3.213449364761907</v>
       </c>
       <c r="G5">
-        <v>-9.407945880170125</v>
+        <v>-8.935322467347152</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.540186964398212</v>
       </c>
       <c r="E6">
-        <v>-16.93225168524955</v>
+        <v>-19.3655592661611</v>
       </c>
       <c r="F6">
-        <v>-2.745147592569859</v>
+        <v>-3.082356081431871</v>
       </c>
       <c r="G6">
-        <v>-9.1124399642437</v>
+        <v>-8.221502638169499</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.703376412820441</v>
       </c>
       <c r="E7">
-        <v>-18.20793187015831</v>
+        <v>-19.30908919528546</v>
       </c>
       <c r="F7">
-        <v>-2.498251031430661</v>
+        <v>-3.02293066068984</v>
       </c>
       <c r="G7">
-        <v>-9.29581439220947</v>
+        <v>-8.438181154260338</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.803819811596351</v>
       </c>
       <c r="E8">
-        <v>-20.61257421060131</v>
+        <v>-18.75209142081601</v>
       </c>
       <c r="F8">
-        <v>-2.358164163208431</v>
+        <v>-3.215821809003525</v>
       </c>
       <c r="G8">
-        <v>-8.853184521972295</v>
+        <v>-8.304441735564861</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.831093565934372</v>
       </c>
       <c r="E9">
-        <v>-20.14076608916415</v>
+        <v>-20.47762568517273</v>
       </c>
       <c r="F9">
-        <v>-2.395030654470023</v>
+        <v>-2.965800646020967</v>
       </c>
       <c r="G9">
-        <v>-8.844633382844357</v>
+        <v>-8.034811043573379</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.772345445690883</v>
       </c>
       <c r="E10">
-        <v>-20.42338362350885</v>
+        <v>-20.74745933739377</v>
       </c>
       <c r="F10">
-        <v>-2.15479333888193</v>
+        <v>-2.994724750624517</v>
       </c>
       <c r="G10">
-        <v>-8.62622676198202</v>
+        <v>-6.994131121666864</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.618872574935972</v>
       </c>
       <c r="E11">
-        <v>-21.30059885200869</v>
+        <v>-21.40359899331315</v>
       </c>
       <c r="F11">
-        <v>-2.318026449073184</v>
+        <v>-3.255133640838181</v>
       </c>
       <c r="G11">
-        <v>-7.202765012097274</v>
+        <v>-7.616060138310967</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.367189602395859</v>
       </c>
       <c r="E12">
-        <v>-20.22880868082128</v>
+        <v>-22.84260765025655</v>
       </c>
       <c r="F12">
-        <v>-2.893113891527518</v>
+        <v>-2.897518321008203</v>
       </c>
       <c r="G12">
-        <v>-6.649122618291718</v>
+        <v>-7.465523011549227</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.016708377358761</v>
       </c>
       <c r="E13">
-        <v>-23.62327128443884</v>
+        <v>-22.61065921158367</v>
       </c>
       <c r="F13">
-        <v>-2.006153577225795</v>
+        <v>-2.984054550109057</v>
       </c>
       <c r="G13">
-        <v>-6.093735566986965</v>
+        <v>-6.199252584960155</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.576374093705746</v>
       </c>
       <c r="E14">
-        <v>-21.76041104579952</v>
+        <v>-22.31559290219189</v>
       </c>
       <c r="F14">
-        <v>-2.312247758071254</v>
+        <v>-2.42675878273205</v>
       </c>
       <c r="G14">
-        <v>-5.765677056772887</v>
+        <v>-6.353156536535334</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.052291545984909</v>
       </c>
       <c r="E15">
-        <v>-25.78510137706456</v>
+        <v>-23.75279469800623</v>
       </c>
       <c r="F15">
-        <v>-1.956447391220811</v>
+        <v>-2.645550494629066</v>
       </c>
       <c r="G15">
-        <v>-5.945373468644527</v>
+        <v>-5.243269660130355</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.457486608188229</v>
       </c>
       <c r="E16">
-        <v>-23.35245948183214</v>
+        <v>-25.29366232080416</v>
       </c>
       <c r="F16">
-        <v>-1.578936343110395</v>
+        <v>-2.451435019294044</v>
       </c>
       <c r="G16">
-        <v>-5.403354400227352</v>
+        <v>-4.786857988813193</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.802643682168154</v>
       </c>
       <c r="E17">
-        <v>-25.4140653877201</v>
+        <v>-25.56606814626156</v>
       </c>
       <c r="F17">
-        <v>-1.905262569401829</v>
+        <v>-2.763015477448245</v>
       </c>
       <c r="G17">
-        <v>-5.164793178121931</v>
+        <v>-4.723937760293804</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.100300313515194</v>
       </c>
       <c r="E18">
-        <v>-26.82836669047765</v>
+        <v>-26.19461128157819</v>
       </c>
       <c r="F18">
-        <v>-1.194281454518236</v>
+        <v>-2.608460344168718</v>
       </c>
       <c r="G18">
-        <v>-5.075911651483578</v>
+        <v>-4.799073901853103</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.3710708600682123</v>
       </c>
       <c r="E19">
-        <v>-26.92756291361567</v>
+        <v>-27.01982151457394</v>
       </c>
       <c r="F19">
-        <v>-1.813731284862095</v>
+        <v>-2.118130626001427</v>
       </c>
       <c r="G19">
-        <v>-4.808902911559199</v>
+        <v>-4.78219011960282</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.367466700283357</v>
       </c>
       <c r="E20">
-        <v>-26.73822288688097</v>
+        <v>-27.45839969374281</v>
       </c>
       <c r="F20">
-        <v>-1.131231926388957</v>
+        <v>-1.822969238138115</v>
       </c>
       <c r="G20">
-        <v>-3.978829965224499</v>
+        <v>-3.461961111269167</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.088391620743842</v>
       </c>
       <c r="E21">
-        <v>-27.39435801432633</v>
+        <v>-27.93204637562707</v>
       </c>
       <c r="F21">
-        <v>-0.7609541824397869</v>
+        <v>-2.01541969499351</v>
       </c>
       <c r="G21">
-        <v>-3.554679560187535</v>
+        <v>-4.114519295242607</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.762893014683059</v>
       </c>
       <c r="E22">
-        <v>-27.96973233631891</v>
+        <v>-28.25026224414607</v>
       </c>
       <c r="F22">
-        <v>-0.8292969782729545</v>
+        <v>-1.827464788033108</v>
       </c>
       <c r="G22">
-        <v>-4.37764476524942</v>
+        <v>-4.290630386295216</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.361147949435907</v>
       </c>
       <c r="E23">
-        <v>-28.67995102883788</v>
+        <v>-28.41503982786317</v>
       </c>
       <c r="F23">
-        <v>-1.014256508704834</v>
+        <v>-2.035536597370497</v>
       </c>
       <c r="G23">
-        <v>-4.325629473736392</v>
+        <v>-3.443637241709301</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.845939285975275</v>
       </c>
       <c r="E24">
-        <v>-26.93252159265407</v>
+        <v>-28.04343777926775</v>
       </c>
       <c r="F24">
-        <v>-0.7094520959055332</v>
+        <v>-1.799311893481564</v>
       </c>
       <c r="G24">
-        <v>-2.9506109367278</v>
+        <v>-3.518041752704421</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.18707937677862</v>
       </c>
       <c r="E25">
-        <v>-28.76207943344099</v>
+        <v>-28.41052493927752</v>
       </c>
       <c r="F25">
-        <v>-0.836124382406828</v>
+        <v>-1.512376193928052</v>
       </c>
       <c r="G25">
-        <v>-3.919028270603104</v>
+        <v>-3.137914982248686</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.35959581987687</v>
       </c>
       <c r="E26">
-        <v>-29.27811263203705</v>
+        <v>-29.10513398189206</v>
       </c>
       <c r="F26">
-        <v>-0.7410775066096127</v>
+        <v>-1.380618559940971</v>
       </c>
       <c r="G26">
-        <v>-3.373946947562104</v>
+        <v>-3.999659917757593</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.343424384458778</v>
       </c>
       <c r="E27">
-        <v>-29.72921883454813</v>
+        <v>-29.21524835586257</v>
       </c>
       <c r="F27">
-        <v>-0.869879525703505</v>
+        <v>-1.477385954833801</v>
       </c>
       <c r="G27">
-        <v>-3.092967705462001</v>
+        <v>-3.345009469003334</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.13380685891334</v>
       </c>
       <c r="E28">
-        <v>-28.21579602847369</v>
+        <v>-28.73834570116679</v>
       </c>
       <c r="F28">
-        <v>-0.7933367209500251</v>
+        <v>-1.747598573259597</v>
       </c>
       <c r="G28">
-        <v>-3.986705753062425</v>
+        <v>-3.493206040068809</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.736876466899741</v>
       </c>
       <c r="E29">
-        <v>-29.65496544624436</v>
+        <v>-28.47271447282486</v>
       </c>
       <c r="F29">
-        <v>-1.129668797099875</v>
+        <v>-1.569151667348527</v>
       </c>
       <c r="G29">
-        <v>-3.471382923873933</v>
+        <v>-3.815298947221121</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.173384474970464</v>
       </c>
       <c r="E30">
-        <v>-30.7218150522894</v>
+        <v>-27.44716907820379</v>
       </c>
       <c r="F30">
-        <v>-0.5311932293948991</v>
+        <v>-1.390395780396213</v>
       </c>
       <c r="G30">
-        <v>-5.050294650100698</v>
+        <v>-4.098294311554639</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.480064720228096</v>
       </c>
       <c r="E31">
-        <v>-29.43606127695058</v>
+        <v>-27.80727333129373</v>
       </c>
       <c r="F31">
-        <v>-0.5993107092945053</v>
+        <v>-1.483078495625839</v>
       </c>
       <c r="G31">
-        <v>-3.871707332664762</v>
+        <v>-3.520584251678581</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.6968334889072196</v>
       </c>
       <c r="E32">
-        <v>-29.29235468279117</v>
+        <v>-28.4323567124685</v>
       </c>
       <c r="F32">
-        <v>-1.345839554534434</v>
+        <v>-1.697455009265934</v>
       </c>
       <c r="G32">
-        <v>-3.058259946028282</v>
+        <v>-4.192641548878329</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.1295530282602179</v>
       </c>
       <c r="E33">
-        <v>-28.43217104503419</v>
+        <v>-28.01609938168344</v>
       </c>
       <c r="F33">
-        <v>-0.2434821779523664</v>
+        <v>-2.183125160792479</v>
       </c>
       <c r="G33">
-        <v>-3.193740711677416</v>
+        <v>-4.075921644800244</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.9509509916465925</v>
       </c>
       <c r="E34">
-        <v>-27.98205431409378</v>
+        <v>-26.02560863161194</v>
       </c>
       <c r="F34">
-        <v>-1.233215550817216</v>
+        <v>-1.531947202186593</v>
       </c>
       <c r="G34">
-        <v>-4.380945379152074</v>
+        <v>-4.156695645412922</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.726509849583277</v>
       </c>
       <c r="E35">
-        <v>-27.88754053307969</v>
+        <v>-26.46573102041742</v>
       </c>
       <c r="F35">
-        <v>-0.3635565180903632</v>
+        <v>-1.710167135429296</v>
       </c>
       <c r="G35">
-        <v>-4.735061193305755</v>
+        <v>-4.226015158459721</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.41668587181471</v>
       </c>
       <c r="E36">
-        <v>-25.54112983990132</v>
+        <v>-26.69566881663089</v>
       </c>
       <c r="F36">
-        <v>-0.6614208687890094</v>
+        <v>-1.242871001264247</v>
       </c>
       <c r="G36">
-        <v>-4.419791320509882</v>
+        <v>-5.073835939430455</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.993424811343173</v>
       </c>
       <c r="E37">
-        <v>-26.53698203045411</v>
+        <v>-25.05848055168981</v>
       </c>
       <c r="F37">
-        <v>-0.3663066978676575</v>
+        <v>-1.484971315141236</v>
       </c>
       <c r="G37">
-        <v>-5.172344532497008</v>
+        <v>-5.253211228384785</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.439214122827909</v>
       </c>
       <c r="E38">
-        <v>-25.15150899322938</v>
+        <v>-26.03507314228797</v>
       </c>
       <c r="F38">
-        <v>0.07242898498366981</v>
+        <v>-1.19555796868595</v>
       </c>
       <c r="G38">
-        <v>-5.917773450483623</v>
+        <v>-5.399779011044939</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.743111654740253</v>
       </c>
       <c r="E39">
-        <v>-25.05781939448469</v>
+        <v>-24.57763812460735</v>
       </c>
       <c r="F39">
-        <v>-0.667178022238466</v>
+        <v>-1.290223795477878</v>
       </c>
       <c r="G39">
-        <v>-5.410064876035454</v>
+        <v>-5.699293997619421</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.909057060243364</v>
       </c>
       <c r="E40">
-        <v>-25.65869808208846</v>
+        <v>-24.01063695105497</v>
       </c>
       <c r="F40">
-        <v>-0.7282535508468735</v>
+        <v>-1.409737330884179</v>
       </c>
       <c r="G40">
-        <v>-5.233394302786708</v>
+        <v>-5.884439567448701</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.946388650714214</v>
       </c>
       <c r="E41">
-        <v>-22.55492275349727</v>
+        <v>-23.24095939481528</v>
       </c>
       <c r="F41">
-        <v>-0.497219397103883</v>
+        <v>-1.365886874049585</v>
       </c>
       <c r="G41">
-        <v>-6.005949830922111</v>
+        <v>-5.382699906607839</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.874944578357633</v>
       </c>
       <c r="E42">
-        <v>-22.8119951659647</v>
+        <v>-23.41880615451852</v>
       </c>
       <c r="F42">
-        <v>-0.8312337012606996</v>
+        <v>-1.27968447701206</v>
       </c>
       <c r="G42">
-        <v>-5.475838794809694</v>
+        <v>-5.159261256525808</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.719746498769706</v>
       </c>
       <c r="E43">
-        <v>-22.94346582335538</v>
+        <v>-22.71115510676189</v>
       </c>
       <c r="F43">
-        <v>-1.157560755919537</v>
+        <v>-1.149489972314061</v>
       </c>
       <c r="G43">
-        <v>-5.902548251548515</v>
+        <v>-6.149660612781873</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.507945341073205</v>
       </c>
       <c r="E44">
-        <v>-23.02669011866835</v>
+        <v>-21.5472738881545</v>
       </c>
       <c r="F44">
-        <v>-0.4053211458047086</v>
+        <v>-1.050388238080142</v>
       </c>
       <c r="G44">
-        <v>-6.049996639322115</v>
+        <v>-5.824968927381233</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.270356080085149</v>
       </c>
       <c r="E45">
-        <v>-22.30381886977194</v>
+        <v>-21.28013014949402</v>
       </c>
       <c r="F45">
-        <v>0.4046010000366604</v>
+        <v>-0.9371205928909493</v>
       </c>
       <c r="G45">
-        <v>-4.619900556176668</v>
+        <v>-6.308937579767289</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.031303278108657</v>
       </c>
       <c r="E46">
-        <v>-22.25522834366964</v>
+        <v>-20.07590022747828</v>
       </c>
       <c r="F46">
-        <v>0.1671834470876969</v>
+        <v>-0.9254613216965463</v>
       </c>
       <c r="G46">
-        <v>-5.31796549913293</v>
+        <v>-5.31024199638981</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.818450149104947</v>
       </c>
       <c r="E47">
-        <v>-20.30349227415578</v>
+        <v>-19.65570312430655</v>
       </c>
       <c r="F47">
-        <v>0.2762396724010574</v>
+        <v>-0.7734045445038634</v>
       </c>
       <c r="G47">
-        <v>-4.958082714649838</v>
+        <v>-6.306236174607244</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.649166432753898</v>
       </c>
       <c r="E48">
-        <v>-19.9526985636256</v>
+        <v>-19.51984437560243</v>
       </c>
       <c r="F48">
-        <v>0.1294065800504282</v>
+        <v>-0.9773519125427128</v>
       </c>
       <c r="G48">
-        <v>-7.07836464236808</v>
+        <v>-7.042418738902674</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.537142273878906</v>
       </c>
       <c r="E49">
-        <v>-19.89139208250976</v>
+        <v>-18.41981464050319</v>
       </c>
       <c r="F49">
-        <v>0.1996504790730207</v>
+        <v>-0.8996833564888284</v>
       </c>
       <c r="G49">
-        <v>-5.348773435921387</v>
+        <v>-6.343757897749343</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.491840308090636</v>
       </c>
       <c r="E50">
-        <v>-16.39060996614012</v>
+        <v>-18.45630961253101</v>
       </c>
       <c r="F50">
-        <v>0.1068294264871277</v>
+        <v>-0.99213412884567</v>
       </c>
       <c r="G50">
-        <v>-5.391525821015536</v>
+        <v>-6.813981165056344</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.509534148110237</v>
       </c>
       <c r="E51">
-        <v>-18.60609341880872</v>
+        <v>-17.75421953085581</v>
       </c>
       <c r="F51">
-        <v>-0.3666786348315145</v>
+        <v>-1.143791632950204</v>
       </c>
       <c r="G51">
-        <v>-6.539090016202961</v>
+        <v>-7.148730287805289</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.591558586274054</v>
       </c>
       <c r="E52">
-        <v>-16.42187907916308</v>
+        <v>-17.4544798362881</v>
       </c>
       <c r="F52">
-        <v>0.1363789484797917</v>
+        <v>-0.770897904742992</v>
       </c>
       <c r="G52">
-        <v>-6.747465684081307</v>
+        <v>-6.761601713533995</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.727410068368601</v>
       </c>
       <c r="E53">
-        <v>-17.76833478433771</v>
+        <v>-15.26562833925862</v>
       </c>
       <c r="F53">
-        <v>0.06768823833744825</v>
+        <v>-0.820965258935597</v>
       </c>
       <c r="G53">
-        <v>-7.1517660580648</v>
+        <v>-6.417248698175624</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.905756501403583</v>
       </c>
       <c r="E54">
-        <v>-17.41302165674788</v>
+        <v>-16.55694534491586</v>
       </c>
       <c r="F54">
-        <v>0.3635669923715841</v>
+        <v>-0.9929194211435239</v>
       </c>
       <c r="G54">
-        <v>-7.017139413164799</v>
+        <v>-6.997372145749811</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.117062143338571</v>
       </c>
       <c r="E55">
-        <v>-15.45078405601023</v>
+        <v>-16.1826080980198</v>
       </c>
       <c r="F55">
-        <v>0.1352747347318599</v>
+        <v>-1.140036643513313</v>
       </c>
       <c r="G55">
-        <v>-6.806486089955434</v>
+        <v>-8.206171501777135</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.343488569345355</v>
       </c>
       <c r="E56">
-        <v>-16.54284820532998</v>
+        <v>-14.68575724257643</v>
       </c>
       <c r="F56">
-        <v>-0.005123599633822694</v>
+        <v>-1.187642918152201</v>
       </c>
       <c r="G56">
-        <v>-7.962876199550556</v>
+        <v>-7.909639316733536</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.577826677580676</v>
       </c>
       <c r="E57">
-        <v>-16.19681844945587</v>
+        <v>-14.96724265841921</v>
       </c>
       <c r="F57">
-        <v>0.4250873542752949</v>
+        <v>-0.8194808245497802</v>
       </c>
       <c r="G57">
-        <v>-8.506166517454812</v>
+        <v>-8.023532014921082</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.808022310733291</v>
       </c>
       <c r="E58">
-        <v>-13.91259728982484</v>
+        <v>-14.52416317608672</v>
       </c>
       <c r="F58">
-        <v>-0.2306814164769057</v>
+        <v>-0.7294298325588489</v>
       </c>
       <c r="G58">
-        <v>-7.668039013823064</v>
+        <v>-7.592091788606644</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.023991670561888</v>
       </c>
       <c r="E59">
-        <v>-14.33048939972667</v>
+        <v>-13.8584910823812</v>
       </c>
       <c r="F59">
-        <v>0.01511838622098603</v>
+        <v>-0.8927267270401181</v>
       </c>
       <c r="G59">
-        <v>-8.25815699838031</v>
+        <v>-8.389492961014277</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.221892099806016</v>
       </c>
       <c r="E60">
-        <v>-14.40841990892467</v>
+        <v>-12.8656412700955</v>
       </c>
       <c r="F60">
-        <v>0.3150462001200058</v>
+        <v>-0.6773984192542063</v>
       </c>
       <c r="G60">
-        <v>-8.452194693528073</v>
+        <v>-8.468578583401927</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.391864878356406</v>
       </c>
       <c r="E61">
-        <v>-13.49293907506002</v>
+        <v>-12.63064063994146</v>
       </c>
       <c r="F61">
-        <v>-0.2411519804482914</v>
+        <v>-0.8280502853317412</v>
       </c>
       <c r="G61">
-        <v>-7.774933218740591</v>
+        <v>-8.788698405412832</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.532958489164431</v>
       </c>
       <c r="E62">
-        <v>-13.80986885696084</v>
+        <v>-11.47303135783469</v>
       </c>
       <c r="F62">
-        <v>0.1406110775406943</v>
+        <v>-0.7972548987652668</v>
       </c>
       <c r="G62">
-        <v>-7.782362082930716</v>
+        <v>-8.87646427820445</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.640013484464791</v>
       </c>
       <c r="E63">
-        <v>-13.61288476610119</v>
+        <v>-12.30214060695104</v>
       </c>
       <c r="F63">
-        <v>-0.3979577879612238</v>
+        <v>-1.213994941970059</v>
       </c>
       <c r="G63">
-        <v>-8.040872652455786</v>
+        <v>-8.168828548094156</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.708328008081596</v>
       </c>
       <c r="E64">
-        <v>-12.86592656395798</v>
+        <v>-11.51975615264583</v>
       </c>
       <c r="F64">
-        <v>0.04695006040836263</v>
+        <v>-1.122470284369547</v>
       </c>
       <c r="G64">
-        <v>-8.069204301180868</v>
+        <v>-8.467628456832156</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.73867576557348</v>
       </c>
       <c r="E65">
-        <v>-12.70530611937992</v>
+        <v>-12.10725772803095</v>
       </c>
       <c r="F65">
-        <v>-0.8546980363123985</v>
+        <v>-1.074058836615138</v>
       </c>
       <c r="G65">
-        <v>-8.9171177774267</v>
+        <v>-9.122626512868038</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.72594660733875</v>
       </c>
       <c r="E66">
-        <v>-12.73437439403516</v>
+        <v>-13.09511263348618</v>
       </c>
       <c r="F66">
-        <v>-0.8281264951327987</v>
+        <v>-1.199071903208626</v>
       </c>
       <c r="G66">
-        <v>-7.974704778762372</v>
+        <v>-8.558171877331223</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.673721581205288</v>
       </c>
       <c r="E67">
-        <v>-12.21078770079431</v>
+        <v>-10.6051674281607</v>
       </c>
       <c r="F67">
-        <v>-0.5555604849156494</v>
+        <v>-1.372506357965355</v>
       </c>
       <c r="G67">
-        <v>-8.756701982775775</v>
+        <v>-8.622641441162989</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.581319006714785</v>
       </c>
       <c r="E68">
-        <v>-12.61031232012102</v>
+        <v>-10.76235528944094</v>
       </c>
       <c r="F68">
-        <v>-0.5744091567989493</v>
+        <v>-1.484717006348576</v>
       </c>
       <c r="G68">
-        <v>-8.542493133657233</v>
+        <v>-8.739007116868372</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.449129654911294</v>
       </c>
       <c r="E69">
-        <v>-12.67905002708345</v>
+        <v>-11.9005374180548</v>
       </c>
       <c r="F69">
-        <v>-0.77774436132713</v>
+        <v>-0.9706653308673152</v>
       </c>
       <c r="G69">
-        <v>-7.803652201293769</v>
+        <v>-8.644262614079969</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.280738595836708</v>
       </c>
       <c r="E70">
-        <v>-12.18363497064431</v>
+        <v>-11.73688742436561</v>
       </c>
       <c r="F70">
-        <v>-0.5724011942145634</v>
+        <v>-1.445449906353671</v>
       </c>
       <c r="G70">
-        <v>-9.001864432686503</v>
+        <v>-8.763359489855251</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.074313536731103</v>
       </c>
       <c r="E71">
-        <v>-13.31619273454065</v>
+        <v>-11.60102414718749</v>
       </c>
       <c r="F71">
-        <v>-0.8259097839629073</v>
+        <v>-1.534669217472192</v>
       </c>
       <c r="G71">
-        <v>-10.15140171301533</v>
+        <v>-8.166325775666467</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.836155600977824</v>
       </c>
       <c r="E72">
-        <v>-12.9501244811826</v>
+        <v>-11.37372192284648</v>
       </c>
       <c r="F72">
-        <v>-0.7949064771783302</v>
+        <v>-1.936519356611663</v>
       </c>
       <c r="G72">
-        <v>-7.958982997996372</v>
+        <v>-7.834675323542279</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.567227950994859</v>
       </c>
       <c r="E73">
-        <v>-13.10802784135606</v>
+        <v>-10.61664710977014</v>
       </c>
       <c r="F73">
-        <v>-0.882939566176042</v>
+        <v>-2.048176655569814</v>
       </c>
       <c r="G73">
-        <v>-6.93564371362456</v>
+        <v>-7.636376956285474</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.271107896660383</v>
       </c>
       <c r="E74">
-        <v>-12.99342122116994</v>
+        <v>-11.93445115989825</v>
       </c>
       <c r="F74">
-        <v>-0.8986015086607723</v>
+        <v>-2.159481898381775</v>
       </c>
       <c r="G74">
-        <v>-8.108795115285012</v>
+        <v>-7.099757387642851</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.952687139028258</v>
       </c>
       <c r="E75">
-        <v>-13.95493399332255</v>
+        <v>-11.44386798522529</v>
       </c>
       <c r="F75">
-        <v>-1.27832346936926</v>
+        <v>-2.20214861819777</v>
       </c>
       <c r="G75">
-        <v>-7.572662196836661</v>
+        <v>-7.566296017764643</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.612311039691491</v>
       </c>
       <c r="E76">
-        <v>-13.92687103989702</v>
+        <v>-12.01303376935335</v>
       </c>
       <c r="F76">
-        <v>-0.6442918876339212</v>
+        <v>-1.910871445086185</v>
       </c>
       <c r="G76">
-        <v>-7.500647899720895</v>
+        <v>-7.823181109429929</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.257289676194217</v>
       </c>
       <c r="E77">
-        <v>-14.24990067628617</v>
+        <v>-13.30720371363542</v>
       </c>
       <c r="F77">
-        <v>-1.224394266344804</v>
+        <v>-2.316449237538253</v>
       </c>
       <c r="G77">
-        <v>-6.453373371100152</v>
+        <v>-7.378174267495557</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.889236350052879</v>
       </c>
       <c r="E78">
-        <v>-14.46474506863207</v>
+        <v>-13.49772567208613</v>
       </c>
       <c r="F78">
-        <v>-1.400069454926106</v>
+        <v>-2.379867389161778</v>
       </c>
       <c r="G78">
-        <v>-6.632410984409476</v>
+        <v>-6.267635213619341</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.513463510021496</v>
       </c>
       <c r="E79">
-        <v>-15.55084068920971</v>
+        <v>-14.68233371622663</v>
       </c>
       <c r="F79">
-        <v>-2.331742556528738</v>
+        <v>-2.526235767399437</v>
       </c>
       <c r="G79">
-        <v>-5.896585959032287</v>
+        <v>-6.743751251986245</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.136032279738303</v>
       </c>
       <c r="E80">
-        <v>-14.66292014815574</v>
+        <v>-14.95540069888915</v>
       </c>
       <c r="F80">
-        <v>-1.660157766954887</v>
+        <v>-2.577211840632913</v>
       </c>
       <c r="G80">
-        <v>-4.812408779285287</v>
+        <v>-6.49530143035502</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.7599330965874707</v>
       </c>
       <c r="E81">
-        <v>-16.46249496253787</v>
+        <v>-14.68478814913878</v>
       </c>
       <c r="F81">
-        <v>-1.894955193808795</v>
+        <v>-2.315550458906216</v>
       </c>
       <c r="G81">
-        <v>-6.584153162083521</v>
+        <v>-6.091974356760073</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.3944332654088378</v>
       </c>
       <c r="E82">
-        <v>-18.41967878628297</v>
+        <v>-15.61691565345563</v>
       </c>
       <c r="F82">
-        <v>-1.621455613528691</v>
+        <v>-2.341729353936889</v>
       </c>
       <c r="G82">
-        <v>-5.692222672347538</v>
+        <v>-5.454277211712421</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.04392462463941275</v>
       </c>
       <c r="E83">
-        <v>-17.77259154990492</v>
+        <v>-16.54089643303267</v>
       </c>
       <c r="F83">
-        <v>-1.727163577799936</v>
+        <v>-3.051957482851337</v>
       </c>
       <c r="G83">
-        <v>-5.431464242401304</v>
+        <v>-5.038303854157457</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.2841643930757476</v>
       </c>
       <c r="E84">
-        <v>-19.8192082068275</v>
+        <v>-17.95239461037947</v>
       </c>
       <c r="F84">
-        <v>-1.962089401601278</v>
+        <v>-3.064218148780173</v>
       </c>
       <c r="G84">
-        <v>-5.316995509289923</v>
+        <v>-4.831182883038495</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.5821771185795978</v>
       </c>
       <c r="E85">
-        <v>-19.50101950915255</v>
+        <v>-18.74636742967031</v>
       </c>
       <c r="F85">
-        <v>-2.208122803906759</v>
+        <v>-3.163532773436611</v>
       </c>
       <c r="G85">
-        <v>-4.44596449354336</v>
+        <v>-4.617828154669084</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.8451686052295577</v>
       </c>
       <c r="E86">
-        <v>-20.70850087550579</v>
+        <v>-20.35780679140378</v>
       </c>
       <c r="F86">
-        <v>-2.185902676694066</v>
+        <v>-3.427581510018176</v>
       </c>
       <c r="G86">
-        <v>-4.586424319683558</v>
+        <v>-5.009382928326384</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.064546051231438</v>
       </c>
       <c r="E87">
-        <v>-21.588301862664</v>
+        <v>-20.23027137792576</v>
       </c>
       <c r="F87">
-        <v>-2.302195519638282</v>
+        <v>-3.804550805847161</v>
       </c>
       <c r="G87">
-        <v>-4.207423134711175</v>
+        <v>-4.58845699464467</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.234420061297507</v>
       </c>
       <c r="E88">
-        <v>-23.92579599052126</v>
+        <v>-21.84399309055909</v>
       </c>
       <c r="F88">
-        <v>-2.805704563184114</v>
+        <v>-3.578822345319101</v>
       </c>
       <c r="G88">
-        <v>-4.637863576272753</v>
+        <v>-3.629901775930855</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.349316476163254</v>
       </c>
       <c r="E89">
-        <v>-24.35839205552599</v>
+        <v>-22.73791838814723</v>
       </c>
       <c r="F89">
-        <v>-2.650474310471307</v>
+        <v>-3.857660753510249</v>
       </c>
       <c r="G89">
-        <v>-4.08848185457624</v>
+        <v>-4.262967467769067</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.402973728411776</v>
       </c>
       <c r="E90">
-        <v>-24.74955258336054</v>
+        <v>-25.38281891706718</v>
       </c>
       <c r="F90">
-        <v>-2.590607369903584</v>
+        <v>-4.08928387647663</v>
       </c>
       <c r="G90">
-        <v>-4.55716240766194</v>
+        <v>-3.470230854026267</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.392700650570123</v>
       </c>
       <c r="E91">
-        <v>-28.35569417599265</v>
+        <v>-26.20794763753078</v>
       </c>
       <c r="F91">
-        <v>-2.600005198088344</v>
+        <v>-4.438569133704055</v>
       </c>
       <c r="G91">
-        <v>-3.749124452436629</v>
+        <v>-4.052214828193524</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.31626124353348</v>
       </c>
       <c r="E92">
-        <v>-29.06560040380509</v>
+        <v>-27.57719062391202</v>
       </c>
       <c r="F92">
-        <v>-3.018946213482375</v>
+        <v>-4.809082962363024</v>
       </c>
       <c r="G92">
-        <v>-4.15829794945393</v>
+        <v>-3.757877534842462</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.172391246264967</v>
       </c>
       <c r="E93">
-        <v>-30.87109393371525</v>
+        <v>-29.12903979617855</v>
       </c>
       <c r="F93">
-        <v>-3.965219290559348</v>
+        <v>-4.648349864993419</v>
       </c>
       <c r="G93">
-        <v>-3.514933150443046</v>
+        <v>-4.121666763061894</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.9646813288804642</v>
       </c>
       <c r="E94">
-        <v>-33.08454636579141</v>
+        <v>-31.09447676380262</v>
       </c>
       <c r="F94">
-        <v>-4.100345066406211</v>
+        <v>-5.096543018482508</v>
       </c>
       <c r="G94">
-        <v>-4.196197074787506</v>
+        <v>-3.929410141414259</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.6968042701573521</v>
       </c>
       <c r="E95">
-        <v>-34.95327324250767</v>
+        <v>-34.23255301876491</v>
       </c>
       <c r="F95">
-        <v>-4.132975286769887</v>
+        <v>-5.184035183566192</v>
       </c>
       <c r="G95">
-        <v>-3.914949678498722</v>
+        <v>-3.787553265056489</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.3701856201031823</v>
       </c>
       <c r="E96">
-        <v>-36.14957154229896</v>
+        <v>-36.42416688493908</v>
       </c>
       <c r="F96">
-        <v>-3.854223028788631</v>
+        <v>-5.399623598716583</v>
       </c>
       <c r="G96">
-        <v>-5.254161354954556</v>
+        <v>-4.858263145549733</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.001248903912071491</v>
       </c>
       <c r="E97">
-        <v>-39.54724709822497</v>
+        <v>-37.67614503689169</v>
       </c>
       <c r="F97">
-        <v>-4.358026142762457</v>
+        <v>-5.573910443530793</v>
       </c>
       <c r="G97">
-        <v>-5.195571320000535</v>
+        <v>-5.207783922494906</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.4238466413990304</v>
       </c>
       <c r="E98">
-        <v>-43.27660167589477</v>
+        <v>-39.66904719937228</v>
       </c>
       <c r="F98">
-        <v>-5.088914583070127</v>
+        <v>-5.764536006997821</v>
       </c>
       <c r="G98">
-        <v>-5.504597503909343</v>
+        <v>-5.840280200500363</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.8702554601035748</v>
       </c>
       <c r="E99">
-        <v>-43.7236005524809</v>
+        <v>-40.98880528603469</v>
       </c>
       <c r="F99">
-        <v>-5.082421839366985</v>
+        <v>-6.397285275993626</v>
       </c>
       <c r="G99">
-        <v>-5.67049887251884</v>
+        <v>-5.496648884069553</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.361773207682472</v>
       </c>
       <c r="E100">
-        <v>-46.22019129341265</v>
+        <v>-44.15701174280702</v>
       </c>
       <c r="F100">
-        <v>-5.110003160410598</v>
+        <v>-6.924766029625371</v>
       </c>
       <c r="G100">
-        <v>-6.784212739567217</v>
+        <v>-7.115651316776892</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.846219060344826</v>
       </c>
       <c r="E101">
-        <v>-48.42251047214095</v>
+        <v>-45.6560498511961</v>
       </c>
       <c r="F101">
-        <v>-4.838478408018767</v>
+        <v>-6.592935301942334</v>
       </c>
       <c r="G101">
-        <v>-6.154335103083324</v>
+        <v>-7.20582395617556</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.393336894607414</v>
       </c>
       <c r="E102">
-        <v>-49.13560361353629</v>
+        <v>-48.24923520694846</v>
       </c>
       <c r="F102">
-        <v>-5.38155524892672</v>
+        <v>-6.654784111521256</v>
       </c>
       <c r="G102">
-        <v>-6.680033181991893</v>
+        <v>-7.382458113423374</v>
       </c>
     </row>
   </sheetData>
